--- a/reports/validation_report.xlsx
+++ b/reports/validation_report.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remaining credits to OJT are valid.</t>
+          <t>Remaining credits to OJT are correct.</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk score is valid.</t>
+          <t>Risk scores are valid.</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eligibility values are valid.</t>
+          <t>OJT eligibility values are valid.</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Recommendation column is valid.</t>
+          <t>AI recommendations are valid.</t>
         </is>
       </c>
     </row>
